--- a/bw_amr_ig/ValueSet-botswana-amr-special-test-vs.xlsx
+++ b/bw_amr_ig/ValueSet-botswana-amr-special-test-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T10:14:37-04:00</t>
+    <t>2026-03-13T15:05:11-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>Methicillin resistant Staphylococcus aureus [Presence] in Specimen</t>
+  </si>
+  <si>
+    <t>6984-4</t>
+  </si>
+  <si>
+    <t>Beta lactamase [Presence] in Isolate</t>
   </si>
   <si>
     <t>System URI</t>
@@ -388,7 +394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -437,18 +443,26 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>37</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/bw_amr_ig/ValueSet-botswana-amr-special-test-vs.xlsx
+++ b/bw_amr_ig/ValueSet-botswana-amr-special-test-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:05:11-04:00</t>
+    <t>2026-03-13T15:54:56-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/bw_amr_ig/ValueSet-botswana-amr-special-test-vs.xlsx
+++ b/bw_amr_ig/ValueSet-botswana-amr-special-test-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-special-test-vs</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-special-test-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:54:56-04:00</t>
+    <t>2026-03-13T21:27:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,28 +105,28 @@
     <t>Extended spectrum beta lactamase [Presence] in Isolate</t>
   </si>
   <si>
-    <t>101214-7</t>
-  </si>
-  <si>
-    <t>Carbapenemase [Presence] in Isolate by Molecular method</t>
-  </si>
-  <si>
-    <t>18895-8</t>
-  </si>
-  <si>
-    <t>Clindamycin inducible resistance [Susceptibility] by Disk diffusion (KB)</t>
-  </si>
-  <si>
-    <t>33747-0</t>
-  </si>
-  <si>
-    <t>Methicillin resistant Staphylococcus aureus [Presence] in Specimen</t>
-  </si>
-  <si>
-    <t>6984-4</t>
-  </si>
-  <si>
-    <t>Beta lactamase [Presence] in Isolate</t>
+    <t>86930-5</t>
+  </si>
+  <si>
+    <t>Carbapenemase [Presence] in Isolate</t>
+  </si>
+  <si>
+    <t>42720-3</t>
+  </si>
+  <si>
+    <t>Clindamycin.induced [Susceptibility] by Disk diffusion (KB)</t>
+  </si>
+  <si>
+    <t>13317-3</t>
+  </si>
+  <si>
+    <t>Methicillin resistant Staphylococcus aureus [Presence] in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>6985-6</t>
+  </si>
+  <si>
+    <t>Beta lactamase.usual [Susceptibility]</t>
   </si>
   <si>
     <t>System URI</t>
